--- a/eoptolink/dist/20261025_新易盛模型_v0.2.1.xlsx
+++ b/eoptolink/dist/20261025_新易盛模型_v0.2.1.xlsx
@@ -6129,7 +6129,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6366,7 +6366,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6487,7 +6487,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6608,7 +6608,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6729,7 +6729,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6850,7 +6850,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
